--- a/output/laminas_comunales/comunal_s_isapre_a_2021_maule.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2021_maule.xlsx
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>31041</v>
+        <v>13.63121377129809</v>
       </c>
     </row>
     <row r="3">
@@ -399,427 +399,427 @@
         </is>
       </c>
       <c r="C3">
-        <v>19550</v>
+        <v>12.00365942763113</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>Constitución</t>
         </is>
       </c>
       <c r="C4">
-        <v>8222</v>
+        <v>8.995322351027049</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="C5">
-        <v>4423</v>
+        <v>8.321220164739094</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Linares</t>
         </is>
       </c>
       <c r="C6">
-        <v>3950</v>
+        <v>8.107841590407068</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Licantén</t>
         </is>
       </c>
       <c r="C7">
-        <v>2615</v>
+        <v>7.228743200687089</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>Pencahue</t>
         </is>
       </c>
       <c r="C8">
-        <v>2338</v>
+        <v>6.18468756664534</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Molina</t>
+          <t>Romeral</t>
         </is>
       </c>
       <c r="C9">
-        <v>2318</v>
+        <v>6.027604682313203</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>Parral</t>
         </is>
       </c>
       <c r="C10">
-        <v>2152</v>
+        <v>5.867306872489848</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>San Clemente</t>
+          <t>Vichuquén</t>
         </is>
       </c>
       <c r="C11">
-        <v>1720</v>
+        <v>5.272852866682017</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Teno</t>
+          <t>Molina</t>
         </is>
       </c>
       <c r="C12">
-        <v>1445</v>
+        <v>4.969876289101864</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Romeral</t>
+          <t>Teno</t>
         </is>
       </c>
       <c r="C13">
-        <v>1035</v>
+        <v>4.943720277806288</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sagrada Familia</t>
+          <t>San Javier</t>
         </is>
       </c>
       <c r="C14">
-        <v>925</v>
+        <v>4.908671005668697</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Colbún</t>
+          <t>Sagrada Familia</t>
         </is>
       </c>
       <c r="C15">
-        <v>826</v>
+        <v>4.893662046344303</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Longaví</t>
+          <t>Cauquenes</t>
         </is>
       </c>
       <c r="C16">
-        <v>758</v>
+        <v>4.811519026964182</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Villa Alegre</t>
+          <t>Pelluhue</t>
         </is>
       </c>
       <c r="C17">
-        <v>642</v>
+        <v>4.615208428767751</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pencahue</t>
+          <t>Rauco</t>
         </is>
       </c>
       <c r="C18">
-        <v>580</v>
+        <v>4.589417788735066</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Retiro</t>
+          <t>Hualañé</t>
         </is>
       </c>
       <c r="C19">
-        <v>560</v>
+        <v>4.462242562929061</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Licantén</t>
+          <t>Curepto</t>
         </is>
       </c>
       <c r="C20">
-        <v>505</v>
+        <v>4.115105087409153</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Río Claro</t>
+          <t>San Rafael</t>
         </is>
       </c>
       <c r="C21">
-        <v>484</v>
+        <v>3.986229389382134</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rauco</t>
+          <t>Villa Alegre</t>
         </is>
       </c>
       <c r="C22">
-        <v>484</v>
+        <v>3.929970617042116</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hualañé</t>
+          <t>San Clemente</t>
         </is>
       </c>
       <c r="C23">
-        <v>468</v>
+        <v>3.794312942577927</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Yerbas Buenas</t>
+          <t>Colbún</t>
         </is>
       </c>
       <c r="C24">
-        <v>457</v>
+        <v>3.751987281399046</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>San Rafael</t>
+          <t>Pelarco</t>
         </is>
       </c>
       <c r="C25">
-        <v>440</v>
+        <v>3.662608012568735</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Curepto</t>
+          <t>Río Claro</t>
         </is>
       </c>
       <c r="C26">
-        <v>419</v>
+        <v>3.38437871477519</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pelluhue</t>
+          <t>Chanco</t>
         </is>
       </c>
       <c r="C27">
-        <v>403</v>
+        <v>3.095290736237011</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pelarco</t>
+          <t>Empedrado</t>
         </is>
       </c>
       <c r="C28">
-        <v>373</v>
+        <v>2.882835228775456</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chanco</t>
+          <t>Retiro</t>
         </is>
       </c>
       <c r="C29">
-        <v>280</v>
+        <v>2.736646630503836</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vichuquén</t>
+          <t>Yerbas Buenas</t>
         </is>
       </c>
       <c r="C30">
-        <v>229</v>
+        <v>2.553928691181401</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Empedrado</t>
+          <t>Longaví</t>
         </is>
       </c>
       <c r="C31">
-        <v>109</v>
+        <v>2.361885769482442</v>
       </c>
     </row>
   </sheetData>
@@ -875,7 +875,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
